--- a/data/trans_orig/Q17H_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q17H_R-Edad-trans_orig.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,25</t>
+          <t>1,02; 1,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,91</t>
+          <t>0,72; 0,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,06</t>
+          <t>0,9; 1,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,85</t>
+          <t>0,72; 0,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,44</t>
+          <t>1,19; 1,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,34</t>
+          <t>0,94; 1,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,27</t>
+          <t>0,23; 0,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,83</t>
+          <t>0,67; 0,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,7</t>
+          <t>0,54; 0,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,14</t>
+          <t>0,98; 1,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 0,99</t>
+          <t>0,79; 1,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,28</t>
+          <t>0,95; 1,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,3</t>
+          <t>1,03; 1,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,47</t>
+          <t>1,07; 1,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,25</t>
+          <t>0,93; 1,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,27 +1022,27 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,87</t>
+          <t>0,61; 0,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,24</t>
+          <t>0,69; 1,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,26</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,12</t>
+          <t>0,88; 1,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,16</t>
+          <t>0,86; 1,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1117,27 +1117,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,12</t>
+          <t>0,72; 1,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,33</t>
+          <t>0,8; 1,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,25</t>
+          <t>0,2; 0,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,95</t>
+          <t>0,56; 0,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,62</t>
+          <t>0,39; 0,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,93</t>
+          <t>0,68; 0,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,92</t>
+          <t>0,61; 0,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,11</t>
+          <t>0,43; 1,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,04</t>
+          <t>0,4; 1,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,67</t>
+          <t>0,38; 0,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,51</t>
+          <t>0,28; 0,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,79</t>
+          <t>0,43; 0,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,71</t>
+          <t>0,36; 0,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,59</t>
+          <t>0,35; 0,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,41</t>
+          <t>0,26; 0,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,54</t>
+          <t>0,3; 0,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,53</t>
+          <t>0,29; 0,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,22</t>
+          <t>0,17; 0,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,44</t>
+          <t>0,3; 0,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,23</t>
+          <t>1,08; 1,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,05</t>
+          <t>0,9; 1,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,67</t>
+          <t>0,55; 0,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,84</t>
+          <t>0,74; 0,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
